--- a/Project2_1/DB산출물/04_테이블정의서.xlsx
+++ b/Project2_1/DB산출물/04_테이블정의서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pknu_202601\day69-day74_미니프로젝트(2차)\project2\PKNU_Project2\Project2_1\DB산출물\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pknu_202601\day69-day74_미니프로젝트(2차)\project2\Project2_1\DB산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4F2D4F-FB87-4784-8673-7192B5E5B637}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D7513F-7BE8-477E-B02B-206ED9BBC421}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="4" xr2:uid="{7B4FFD32-6000-4470-9C7F-42EB358F027C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="1" xr2:uid="{7B4FFD32-6000-4470-9C7F-42EB358F027C}"/>
   </bookViews>
   <sheets>
     <sheet name="Member" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="150">
   <si>
     <t>테이블정의서</t>
   </si>
@@ -218,10 +218,6 @@
     <t xml:space="preserve">HE_chol </t>
   </si>
   <si>
-    <t>HE_TG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HE_BMI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -265,9 +261,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>중성지방</t>
-  </si>
-  <si>
     <t>체질량지수</t>
   </si>
   <si>
@@ -297,10 +290,6 @@
   </si>
   <si>
     <t>NUMBER(5,1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NUMBER(6,1)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -683,7 +672,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -899,13 +888,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -945,6 +1007,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -966,42 +1067,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1011,21 +1076,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1043,6 +1093,66 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1374,50 +1484,50 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1"/>
     <row r="2" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="27" t="s">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -1445,7 +1555,7 @@
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -1460,7 +1570,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -1474,12 +1584,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
@@ -1495,25 +1605,25 @@
         <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>22</v>
@@ -1522,10 +1632,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -1544,49 +1654,49 @@
         <v>29</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="11">
         <v>4</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G7:J7"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:J6"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1596,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AE0AA4-CB13-4D0B-9558-40535FA8F1BE}">
-  <dimension ref="A2:J35"/>
+  <dimension ref="A2:J34"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="14.375" bestFit="1" customWidth="1"/>
@@ -1609,50 +1719,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="27" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -1660,7 +1770,7 @@
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
@@ -1680,7 +1790,7 @@
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -1695,7 +1805,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -1709,19 +1819,19 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
@@ -1735,10 +1845,10 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10" ht="17.25">
       <c r="A9" s="2">
@@ -1759,12 +1869,12 @@
       <c r="F9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -1781,10 +1891,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="15"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" spans="1:10" ht="17.25">
       <c r="A11" s="2">
@@ -1801,12 +1911,12 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2">
@@ -1823,12 +1933,12 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="15"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2">
@@ -1845,12 +1955,12 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="15"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2">
@@ -1867,12 +1977,12 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2">
@@ -1889,12 +1999,12 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="34"/>
+      <c r="G15" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:10" ht="17.25">
       <c r="A16" s="2">
@@ -1904,17 +2014,17 @@
         <v>49</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="17.25">
       <c r="A17" s="2">
@@ -1924,17 +2034,17 @@
         <v>50</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2">
@@ -1944,346 +2054,357 @@
         <v>51</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="15"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="17.25">
-      <c r="A19" s="2">
+      <c r="A19" s="13">
         <v>12</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
+    </row>
+    <row r="20" spans="1:10" ht="17.25">
+      <c r="A20" s="13">
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" spans="1:10" ht="17.25">
-      <c r="A20" s="2">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="28"/>
+    </row>
+    <row r="21" spans="1:10" ht="214.5" customHeight="1">
+      <c r="A21" s="6">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10" ht="17.25">
-      <c r="A21" s="2">
-        <v>14</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="28"/>
+    </row>
+    <row r="22" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A22" s="51">
+        <v>15</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="55"/>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A23" s="52"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="58"/>
+    </row>
+    <row r="24" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A24" s="6">
+        <v>16</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="35"/>
+    </row>
+    <row r="25" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A25" s="51">
+        <v>17</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="1:10" ht="17.25">
-      <c r="A22" s="6">
-        <v>15</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="D25" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="44"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="59"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="47"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="59"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="47"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="50"/>
+    </row>
+    <row r="29" spans="1:10" ht="17.25">
+      <c r="A29" s="6">
+        <v>18</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="37"/>
-    </row>
-    <row r="23" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A23" s="16">
-        <v>16</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="6">
-        <v>17</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="32" t="s">
+      <c r="D29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="34"/>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A26" s="16">
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="13">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="6">
+        <v>20</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="D31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="13">
+        <v>21</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-    </row>
-    <row r="30" spans="1:10" ht="17.25">
-      <c r="A30" s="6">
-        <v>19</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2">
-        <v>20</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="6">
-        <v>21</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>24</v>
+      <c r="D32" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="15"/>
+      <c r="G32" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="28"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="2">
+      <c r="A33" s="13">
         <v>22</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="15"/>
+      <c r="G33" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="28"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2">
         <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="2">
-        <v>24</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="15"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="G35:J35"/>
+  <mergeCells count="47">
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="F25:F28"/>
     <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G25:J28"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="A2:J3"/>
     <mergeCell ref="A4:B4"/>
@@ -2298,38 +2419,6 @@
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G26:J29"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="G32:J32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2348,50 +2437,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="27" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -2399,7 +2488,7 @@
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
@@ -2414,27 +2503,27 @@
       <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="43"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>8</v>
@@ -2448,22 +2537,22 @@
       <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="44" t="s">
+      <c r="G7" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>39</v>
@@ -2474,10 +2563,10 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="15"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:10" ht="17.25">
       <c r="A9" s="2">
@@ -2487,149 +2576,144 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="15"/>
+        <v>93</v>
+      </c>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="15"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="10">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="15"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="15"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="9">
         <v>7</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9">
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="15"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G12:J12"/>
@@ -2645,6 +2729,11 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G10:J10"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2664,50 +2753,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="27" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -2715,7 +2804,7 @@
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
@@ -2735,7 +2824,7 @@
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -2750,7 +2839,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -2764,22 +2853,22 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>39</v>
@@ -2788,12 +2877,12 @@
         <v>29</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
+        <v>125</v>
+      </c>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2">
@@ -2803,7 +2892,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
@@ -2812,22 +2901,22 @@
         <v>28</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
+        <v>125</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
@@ -2838,40 +2927,33 @@
       <c r="F10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G10:J10"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
@@ -2881,6 +2963,13 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2899,50 +2988,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -2950,7 +3039,7 @@
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
@@ -2970,7 +3059,7 @@
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -2985,7 +3074,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -2999,22 +3088,22 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="12">
         <v>1</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>142</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>145</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>39</v>
@@ -3025,10 +3114,10 @@
       <c r="F8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="12">
@@ -3038,7 +3127,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>26</v>
@@ -3049,22 +3138,22 @@
       <c r="F9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="12">
         <v>3</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>26</v>
@@ -3073,65 +3162,65 @@
         <v>29</v>
       </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="12">
         <v>4</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="12"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="10">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="G12:J12"/>
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:J6"/>

--- a/Project2_1/DB산출물/04_테이블정의서.xlsx
+++ b/Project2_1/DB산출물/04_테이블정의서.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pknu_202601\day69-day74_미니프로젝트(2차)\project2\Project2_1\DB산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D7513F-7BE8-477E-B02B-206ED9BBC421}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325C7DC0-1EAE-413C-9156-4A61A3B97AF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="1" xr2:uid="{7B4FFD32-6000-4470-9C7F-42EB358F027C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="4" xr2:uid="{7B4FFD32-6000-4470-9C7F-42EB358F027C}"/>
   </bookViews>
   <sheets>
     <sheet name="Member" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="Community" sheetId="3" r:id="rId3"/>
-    <sheet name="COMMENT" sheetId="4" r:id="rId4"/>
-    <sheet name="INQUIRY" sheetId="5" r:id="rId5"/>
+    <sheet name="Comment" sheetId="4" r:id="rId4"/>
+    <sheet name="Inquiry" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1013,6 +1013,45 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1028,44 +1067,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1076,6 +1091,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1093,66 +1153,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1484,86 +1484,86 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1"/>
     <row r="2" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="16" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
+      <c r="H4" s="30"/>
+      <c r="I4" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="17"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="20" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
@@ -1584,12 +1584,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="32"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
@@ -1610,10 +1610,10 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2">
@@ -1632,10 +1632,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -1654,10 +1654,10 @@
         <v>29</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="11">
@@ -1674,29 +1674,29 @@
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="28"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:J6"/>
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G7:J7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1719,86 +1719,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="16" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
+      <c r="H4" s="30"/>
+      <c r="I4" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="17"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="20" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
@@ -1819,12 +1819,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="32"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
@@ -1845,10 +1845,10 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" ht="17.25">
       <c r="A9" s="2">
@@ -1869,12 +1869,12 @@
       <c r="F9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -1891,10 +1891,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" ht="17.25">
       <c r="A11" s="2">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="28"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="28"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="28"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" ht="17.25">
       <c r="A16" s="2">
@@ -2021,10 +2021,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="28"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="17.25">
       <c r="A17" s="2">
@@ -2041,10 +2041,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="28"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="17"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2">
@@ -2061,10 +2061,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="28"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="17"/>
     </row>
     <row r="19" spans="1:10" ht="17.25">
       <c r="A19" s="13">
@@ -2081,10 +2081,10 @@
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="28"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" ht="17.25">
       <c r="A20" s="13">
@@ -2101,10 +2101,10 @@
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="28"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" ht="214.5" customHeight="1">
       <c r="A21" s="6">
@@ -2121,46 +2121,46 @@
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="28"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="17"/>
     </row>
     <row r="22" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A22" s="51">
+      <c r="A22" s="33">
         <v>15</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="60" t="s">
+      <c r="D22" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="53" t="s">
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="55"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="43"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A23" s="52"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="58"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:10" ht="16.5" customHeight="1">
       <c r="A24" s="6">
@@ -2177,70 +2177,70 @@
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
-      <c r="G24" s="33" t="s">
+      <c r="G24" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="35"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="40"/>
     </row>
     <row r="25" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A25" s="51">
+      <c r="A25" s="33">
         <v>17</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="D25" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="42" t="s">
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="44"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="49"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="59"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="47"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="52"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="59"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="47"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="52"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="52"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="50"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="55"/>
     </row>
     <row r="29" spans="1:10" ht="17.25">
       <c r="A29" s="6">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
-      <c r="G29" s="26" t="s">
+      <c r="G29" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="28"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="17"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="13">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="28"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="6">
@@ -2301,10 +2301,10 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="28"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="17"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="13">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="28"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="17"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="13">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="26" t="s">
+      <c r="G33" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="28"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="17"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2">
@@ -2365,13 +2365,52 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="28"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G25:J28"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
     <mergeCell ref="G30:J30"/>
     <mergeCell ref="G29:J29"/>
     <mergeCell ref="G33:J33"/>
@@ -2380,45 +2419,6 @@
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="C25:C28"/>
     <mergeCell ref="G31:J31"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G25:J28"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2437,86 +2437,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="16" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
+      <c r="H4" s="30"/>
+      <c r="I4" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="17"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="20" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="39"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="59"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="7" t="s">
@@ -2537,12 +2537,12 @@
       <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
@@ -2563,10 +2563,10 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="28"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" ht="17.25">
       <c r="A9" s="2">
@@ -2587,10 +2587,10 @@
       <c r="F9" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="28"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="17"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -2607,10 +2607,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2">
@@ -2627,10 +2627,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="28"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="10">
@@ -2647,10 +2647,10 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2">
@@ -2667,10 +2667,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="28"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="9">
@@ -2687,10 +2687,10 @@
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="28"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9">
@@ -2707,13 +2707,18 @@
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="28"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G12:J12"/>
@@ -2729,11 +2734,6 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G10:J10"/>
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2753,86 +2753,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="16" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
+      <c r="H4" s="30"/>
+      <c r="I4" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="17"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="20" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
@@ -2853,12 +2853,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="32"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
@@ -2879,10 +2879,10 @@
       <c r="F8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2">
@@ -2903,10 +2903,10 @@
       <c r="F9" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -2927,10 +2927,10 @@
       <c r="F10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2">
@@ -2947,13 +2947,20 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="28"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
@@ -2963,13 +2970,6 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G10:J10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2988,86 +2988,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="16" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
+      <c r="H4" s="30"/>
+      <c r="I4" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="J4" s="17"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="20" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
@@ -3088,12 +3088,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="32"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="12">
@@ -3114,10 +3114,10 @@
       <c r="F8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="12">
@@ -3138,12 +3138,12 @@
       <c r="F9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="12">
@@ -3162,10 +3162,10 @@
         <v>29</v>
       </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="12">
@@ -3184,10 +3184,10 @@
         <v>29</v>
       </c>
       <c r="F11" s="12"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="28"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="10">
@@ -3204,18 +3204,13 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
@@ -3228,6 +3223,11 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G10:J10"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Project2_1/DB산출물/04_테이블정의서.xlsx
+++ b/Project2_1/DB산출물/04_테이블정의서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pknu_202601\day69-day74_미니프로젝트(2차)\project2\Project2_1\DB산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325C7DC0-1EAE-413C-9156-4A61A3B97AF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30ECA65A-9EA7-43AB-82E4-6ECFB44A50CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="4" xr2:uid="{7B4FFD32-6000-4470-9C7F-42EB358F027C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="1" xr2:uid="{7B4FFD32-6000-4470-9C7F-42EB358F027C}"/>
   </bookViews>
   <sheets>
     <sheet name="Member" sheetId="1" r:id="rId1"/>
@@ -1013,6 +1013,39 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1034,38 +1067,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1076,65 +1085,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1484,86 +1484,86 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1"/>
     <row r="2" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29" t="s">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="31" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="22" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24" t="s">
+      <c r="H5" s="21"/>
+      <c r="I5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="27"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
@@ -1584,12 +1584,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="21"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
@@ -1610,10 +1610,10 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2">
@@ -1632,10 +1632,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -1654,10 +1654,10 @@
         <v>29</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="11">
@@ -1674,29 +1674,29 @@
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G7:J7"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:J6"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1719,86 +1719,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29" t="s">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="31" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="22" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24" t="s">
+      <c r="H5" s="21"/>
+      <c r="I5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="27"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
@@ -1819,12 +1819,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="21"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
@@ -1845,10 +1845,10 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10" ht="17.25">
       <c r="A9" s="2">
@@ -1869,12 +1869,12 @@
       <c r="F9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -1891,10 +1891,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="17"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" spans="1:10" ht="17.25">
       <c r="A11" s="2">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="17"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="38" t="s">
+      <c r="G15" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="40"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:10" ht="17.25">
       <c r="A16" s="2">
@@ -2021,10 +2021,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="17"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="17.25">
       <c r="A17" s="2">
@@ -2041,10 +2041,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="17"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2">
@@ -2061,10 +2061,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="17"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="17.25">
       <c r="A19" s="13">
@@ -2081,10 +2081,10 @@
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="17"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="17.25">
       <c r="A20" s="13">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" ht="214.5" customHeight="1">
+      <c r="G20" s="26"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="28"/>
+    </row>
+    <row r="21" spans="1:10" ht="27" customHeight="1">
       <c r="A21" s="6">
         <v>14</v>
       </c>
@@ -2121,46 +2121,46 @@
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="17"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A22" s="33">
+      <c r="A22" s="36">
         <v>15</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="41" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="43"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="41"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="44"/>
     </row>
     <row r="24" spans="1:10" ht="16.5" customHeight="1">
       <c r="A24" s="6">
@@ -2177,70 +2177,70 @@
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="40"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="35"/>
     </row>
     <row r="25" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A25" s="33">
+      <c r="A25" s="36">
         <v>17</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="47" t="s">
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="49"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="47"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="52"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="50"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="34"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="52"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="50"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="35"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="55"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="53"/>
     </row>
     <row r="29" spans="1:10" ht="17.25">
       <c r="A29" s="6">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="17"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="28"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="13">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="17"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="28"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="6">
@@ -2301,10 +2301,10 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="17"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="13">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="17"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="28"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="13">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="17"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="28"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2">
@@ -2365,26 +2365,31 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="17"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G25:J28"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G17:J17"/>
@@ -2399,26 +2404,21 @@
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G24:J24"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G25:J28"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
     <mergeCell ref="G30:J30"/>
     <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:J6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2437,76 +2437,76 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29" t="s">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="31" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="22" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24" t="s">
+      <c r="H5" s="21"/>
+      <c r="I5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="21"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="57" t="s">
         <v>91</v>
       </c>
@@ -2563,10 +2563,10 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="17"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:10" ht="17.25">
       <c r="A9" s="2">
@@ -2587,10 +2587,10 @@
       <c r="F9" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="17"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -2607,10 +2607,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="17"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2">
@@ -2627,10 +2627,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="10">
@@ -2647,10 +2647,10 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="17"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2">
@@ -2667,10 +2667,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="9">
@@ -2687,10 +2687,10 @@
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9">
@@ -2707,18 +2707,13 @@
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G12:J12"/>
@@ -2734,6 +2729,11 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G10:J10"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2753,86 +2753,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29" t="s">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="31" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="22" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24" t="s">
+      <c r="H5" s="21"/>
+      <c r="I5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="27"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
@@ -2853,12 +2853,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="21"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2">
@@ -2879,10 +2879,10 @@
       <c r="F8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2">
@@ -2903,10 +2903,10 @@
       <c r="F9" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2">
@@ -2927,10 +2927,10 @@
       <c r="F10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2">
@@ -2947,20 +2947,13 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G10:J10"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
@@ -2970,6 +2963,13 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2988,86 +2988,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29" t="s">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="31" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="22" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24" t="s">
+      <c r="H5" s="21"/>
+      <c r="I5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="27"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
@@ -3088,12 +3088,12 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="21"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="12">
@@ -3114,10 +3114,10 @@
       <c r="F8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="12">
@@ -3138,12 +3138,12 @@
       <c r="F9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="12">
@@ -3162,10 +3162,10 @@
         <v>29</v>
       </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="12">
@@ -3184,10 +3184,10 @@
         <v>29</v>
       </c>
       <c r="F11" s="12"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="10">
@@ -3204,13 +3204,18 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
@@ -3223,11 +3228,6 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G10:J10"/>
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
